--- a/payment_forms/023_stripe_product_order_form--payment_forms.xlsx
+++ b/payment_forms/023_stripe_product_order_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>payment method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>order_comments</t>
+          <t>order_comments_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>order comments</t>
+          <t>Order Comments 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>order_status</t>
+          <t>order_status_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>order status</t>
+          <t>Order Status 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>order_status_choices</t>
+          <t>order_status_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
